--- a/src/test/java/ServiceNow/CHARMS/Resources/RASScenario2.xlsx
+++ b/src/test/java/ServiceNow/CHARMS/Resources/RASScenario2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juarezds/Desktop/CBIIT-Test-Automation/src/test/java/ServiceNow/CHARMS/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F171E7F5-29FD-9C48-AC06-30EDD2C2E006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FF8281-4F3C-6141-B877-2D35A3D6C2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39520" yWindow="940" windowWidth="38880" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="screenerScenario2" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="3144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="3145">
   <si>
     <t>Question</t>
   </si>
@@ -9630,6 +9630,9 @@
   </si>
   <si>
     <t>For which specific RASopathy have you been diagnosed? Other text box</t>
+  </si>
+  <si>
+    <t>Asian</t>
   </si>
 </sst>
 </file>
@@ -10308,7 +10311,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>33</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -24280,18 +24283,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24314,18 +24317,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A376A26F-A459-4EA6-9FC7-DF620BE07CA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B75DB3A7-FCD6-4DD2-8F1A-F1A891316494}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A376A26F-A459-4EA6-9FC7-DF620BE07CA9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>